--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575520.7593602017</v>
+        <v>575521</v>
       </c>
       <c r="R2" t="n">
-        <v>6371441.86579792</v>
+        <v>6371442</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>99950</v>
+        <v>99955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>99955</v>
+        <v>99956</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>99956</v>
+        <v>99983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>99983</v>
+        <v>99989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>99989</v>
+        <v>99996</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>99996</v>
+        <v>100000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>100000</v>
+        <v>100007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>100010</v>
+        <v>100015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>100015</v>
+        <v>100023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>100023</v>
+        <v>100033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>92809117</v>
       </c>
       <c r="B2" t="n">
-        <v>100033</v>
+        <v>100493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,55 +786,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100440284</v>
+        <v>120679744</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>706</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vimmerby, Sm</t>
+          <t>Appeltorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575386.5753142096</v>
+        <v>575571</v>
       </c>
       <c r="R3" t="n">
-        <v>6371472.183431993</v>
+        <v>6371393</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,22 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sören Mjösberg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,77 +882,70 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Hygge</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Åke Rühling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Via Åke Rühling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120679744</v>
+        <v>100440284</v>
       </c>
       <c r="B4" t="n">
-        <v>103104</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>706</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Appeltorp, Sm</t>
+          <t>Vimmerby, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575571</v>
+        <v>575387</v>
       </c>
       <c r="R4" t="n">
-        <v>6371393</v>
+        <v>6371472</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,17 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sören Mjösberg</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,20 +986,15 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Hygge</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Åke Rühling</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 73602-2021 artfynd.xlsx
+++ b/artfynd/A 73602-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92809117</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679744</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,8 +1013,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100440284</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>